--- a/storage/templates/Template_inv.xlsx
+++ b/storage/templates/Template_inv.xlsx
@@ -1,47 +1,67 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alfonsus Vega\Documents\GitHub\sinerco\storage\templates\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAE12399-95E7-4A3E-9EFE-0F35CBC3251A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Rekap Inv" sheetId="8" r:id="rId1"/>
-    <sheet name="7116" sheetId="10" r:id="rId2"/>
+    <sheet name="Rekap Inv" sheetId="1" r:id="rId4"/>
+    <sheet name="7116" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Rekap Inv'!$A$1:$E$16</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'7116'!$A$1:$T$37</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Rekap Inv'!$A$1:$E$16</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="60">
+  <si>
+    <t>Tanggal awal tagihan</t>
+  </si>
+  <si>
+    <t>{{start_date}}</t>
+  </si>
+  <si>
+    <t>HSPHK</t>
+  </si>
+  <si>
+    <t>Standby rate / day</t>
+  </si>
+  <si>
+    <t>Total invoice</t>
+  </si>
+  <si>
+    <t>IDR</t>
+  </si>
+  <si>
+    <t>{{unit_sn}}</t>
+  </si>
+  <si>
+    <t>{{price_unit_sn}}</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>{{total_price}}</t>
+  </si>
+  <si>
+    <t>Pihak kesatu</t>
+  </si>
+  <si>
+    <t>Pihak Kedua</t>
+  </si>
+  <si>
+    <t>Nama</t>
+  </si>
+  <si>
+    <t>Departemen</t>
+  </si>
   <si>
     <t>MONTHLY GAS COMPRESSION REPORT</t>
   </si>
@@ -49,328 +69,290 @@
     <t>GasJack Compressor</t>
   </si>
   <si>
+    <t>HSPHK :</t>
+  </si>
+  <si>
+    <t>Unit S/N</t>
+  </si>
+  <si>
+    <t>Standby rate / day :</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
+    <t>P Source</t>
+  </si>
+  <si>
+    <t>P Suct.</t>
+  </si>
+  <si>
+    <t>P Disch.</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>Perf.</t>
+  </si>
+  <si>
+    <t>Curve</t>
+  </si>
+  <si>
+    <t>T Disch.</t>
+  </si>
+  <si>
+    <t>Speed</t>
+  </si>
+  <si>
+    <t>Liquid Gain</t>
+  </si>
+  <si>
+    <t>Operating Time</t>
+  </si>
+  <si>
+    <t>Run</t>
+  </si>
+  <si>
+    <t>Availability</t>
+  </si>
+  <si>
+    <t>Operating Time (hrs)</t>
+  </si>
+  <si>
     <t>Nilai</t>
   </si>
   <si>
     <t>Remarks</t>
   </si>
   <si>
+    <t>Standby berturut-turut bulan sebelumnya :</t>
+  </si>
+  <si>
+    <t>hari</t>
+  </si>
+  <si>
+    <t>psig</t>
+  </si>
+  <si>
+    <t>{{suction_press_unit}}</t>
+  </si>
+  <si>
+    <t>{{disharge_press_unit}}</t>
+  </si>
+  <si>
+    <t>MSCF</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>MSCFD</t>
+  </si>
+  <si>
+    <t>°F</t>
+  </si>
+  <si>
+    <t>RPM</t>
+  </si>
+  <si>
+    <t>BPD</t>
+  </si>
+  <si>
+    <t>Standby</t>
+  </si>
+  <si>
+    <t>Down</t>
+  </si>
+  <si>
+    <t>HSPHA</t>
+  </si>
+  <si>
+    <t>Curve / BA</t>
+  </si>
+  <si>
+    <t>{{date}}</t>
+  </si>
+  <si>
+    <t>{{suction_press}}</t>
+  </si>
+  <si>
+    <t>{{discharge_press}}</t>
+  </si>
+  <si>
+    <t>{{flowrate}}</t>
+  </si>
+  <si>
+    <t>{{run}}</t>
+  </si>
+  <si>
+    <t>{{stby}}</t>
+  </si>
+  <si>
+    <t>{{down}}</t>
+  </si>
+  <si>
+    <t>{{remarks}}</t>
+  </si>
+  <si>
+    <t>BA</t>
+  </si>
+  <si>
     <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Total invoice</t>
-  </si>
-  <si>
-    <t>IDR</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Pihak kesatu</t>
-  </si>
-  <si>
-    <t>Pihak Kedua</t>
-  </si>
-  <si>
-    <t>psig</t>
-  </si>
-  <si>
-    <t>MSCFD</t>
-  </si>
-  <si>
-    <t>%</t>
-  </si>
-  <si>
-    <t>P Source</t>
-  </si>
-  <si>
-    <t>P Suct.</t>
-  </si>
-  <si>
-    <t>P Disch.</t>
-  </si>
-  <si>
-    <t>Volume</t>
-  </si>
-  <si>
-    <t>Perf.</t>
-  </si>
-  <si>
-    <t>Curve</t>
-  </si>
-  <si>
-    <t>T Disch.</t>
-  </si>
-  <si>
-    <t>Speed</t>
-  </si>
-  <si>
-    <t>Liquid Gain</t>
-  </si>
-  <si>
-    <t>Operating Time (hrs)</t>
-  </si>
-  <si>
-    <t>Run</t>
-  </si>
-  <si>
-    <t>Availability</t>
-  </si>
-  <si>
-    <t>MSCF</t>
-  </si>
-  <si>
-    <t>°F</t>
-  </si>
-  <si>
-    <t>RPM</t>
-  </si>
-  <si>
-    <t>BPD</t>
-  </si>
-  <si>
-    <t>Standby</t>
-  </si>
-  <si>
-    <t>Down</t>
-  </si>
-  <si>
-    <t>Unit S/N</t>
-  </si>
-  <si>
-    <t>Tanggal awal tagihan</t>
-  </si>
-  <si>
-    <t>Standby rate / day :</t>
-  </si>
-  <si>
-    <t>Standby rate / day</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Operating Time</t>
-  </si>
-  <si>
-    <t>hari</t>
-  </si>
-  <si>
-    <t>Standby berturut-turut bulan sebelumnya :</t>
-  </si>
-  <si>
-    <t>HSPHA</t>
-  </si>
-  <si>
-    <t>HSPHK :</t>
-  </si>
-  <si>
-    <t>HSPHK</t>
-  </si>
-  <si>
-    <t>Curve / BA</t>
-  </si>
-  <si>
-    <t>BA</t>
-  </si>
-  <si>
-    <t>{{unit_sn}}</t>
-  </si>
-  <si>
-    <t>{{suction_press}}</t>
-  </si>
-  <si>
-    <t>{{disharge_press_unit}}</t>
-  </si>
-  <si>
-    <t>{{suction_press_unit}}</t>
-  </si>
-  <si>
-    <t>{{date}}</t>
-  </si>
-  <si>
-    <t>{{discharge_press}}</t>
-  </si>
-  <si>
-    <t>{{flowrate}}</t>
-  </si>
-  <si>
-    <t>{{run}}</t>
-  </si>
-  <si>
-    <t>{{stby}}</t>
-  </si>
-  <si>
-    <t>{{down}}</t>
-  </si>
-  <si>
-    <t>{{remarks}}</t>
-  </si>
-  <si>
-    <t>{{start_date}}</t>
-  </si>
-  <si>
-    <t>{{price_unit_sn}}</t>
-  </si>
-  <si>
-    <t>{{total_price}}</t>
-  </si>
-  <si>
-    <t>Nama</t>
-  </si>
-  <si>
-    <t>Departemen</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="11">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="10">
+    <numFmt numFmtId="164" formatCode="\:\ @"/>
     <numFmt numFmtId="165" formatCode="_(&quot;Rp&quot;* #,##0_);_(&quot;Rp&quot;* \(#,##0\);_(&quot;Rp&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="\:\ @"/>
-    <numFmt numFmtId="167" formatCode="[$-409]d\ mmm;@"/>
-    <numFmt numFmtId="168" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="169" formatCode="[hh]:mm"/>
-    <numFmt numFmtId="170" formatCode="[$Rp-3809]#,##0.0"/>
-    <numFmt numFmtId="171" formatCode="0.00_)"/>
-    <numFmt numFmtId="172" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="173" formatCode="&quot;Biaya&quot;\ [$-421]\ mmmm\ yyyy"/>
-    <numFmt numFmtId="174" formatCode="[$-421]d\ mmm\ yyyy;@"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="167" formatCode="[hh]:mm"/>
+    <numFmt numFmtId="168" formatCode="[$-409]d\ mmm;@"/>
+    <numFmt numFmtId="169" formatCode="[$Rp-3809]#,##0.0"/>
+    <numFmt numFmtId="170" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="171" formatCode="[$-421]d\ mmm\ yyyy;@"/>
+    <numFmt numFmtId="172" formatCode="&quot;Biaya&quot;\ [$-421]\ mmmm\ yyyy"/>
+    <numFmt numFmtId="173" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="15">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-      <scheme val="minor"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
     <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-      <scheme val="minor"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
     <font>
-      <u/>
-      <sz val="14"/>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="14"/>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="single"/>
       <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF006600"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
-      <b/>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF006600"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="single"/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Courier New"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Courier"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="14"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF00B050"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF00B050"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -382,20 +364,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="9"/>
-        <bgColor indexed="26"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -409,69 +391,7 @@
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right/>
       <top/>
@@ -481,7 +401,7 @@
     <border>
       <left/>
       <right style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top/>
       <bottom/>
@@ -489,42 +409,59 @@
     </border>
     <border>
       <left style="medium">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="medium">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
       </left>
       <right/>
       <top style="medium">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -532,560 +469,577 @@
       <left/>
       <right/>
       <top style="medium">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="true" diagonalDown="false">
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal style="thin">
+        <color rgb="FF000000"/>
+      </diagonal>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="medium">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
       </right>
       <top style="medium">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
-      <right style="medium">
-        <color auto="1"/>
+      <right style="thin">
+        <color rgb="FF000000"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
       <bottom style="medium">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="1">
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="thin">
-        <color auto="1"/>
-      </diagonal>
-    </border>
   </borders>
-  <cellStyleXfs count="11">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="15" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="100">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="10" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="10" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="16" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="16" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="16" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="10" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="16" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="10" fontId="9" fillId="3" borderId="10" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="10" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="18" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="18" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="18" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="18" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="10" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="12" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="12" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="10" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="174" fontId="5" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="10" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="10" fontId="9" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="10" fontId="9" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="10" fontId="9" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="168" fontId="19" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="10" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="6" fillId="0" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="6" fillId="0" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="5" fillId="0" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="5" fillId="0" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="164" fillId="2" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="165" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="4" fillId="0" borderId="3" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="166" fillId="0" borderId="3" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="4" fillId="0" borderId="3" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="3" fillId="0" borderId="3" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="167" fillId="0" borderId="5" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="4" fillId="0" borderId="5" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="166" fillId="0" borderId="5" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="4" fillId="0" borderId="5" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="3" fillId="0" borderId="5" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="167" fillId="0" borderId="3" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" quotePrefix="1" numFmtId="168" fillId="0" borderId="5" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="10" fillId="3" borderId="3" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="2" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="169" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="165" fillId="0" borderId="3" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="true">
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="170" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="3" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="true">
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" quotePrefix="1" numFmtId="168" fillId="0" borderId="9" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="4" fillId="0" borderId="9" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="4" fillId="0" borderId="9" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="166" fillId="0" borderId="9" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="3" fillId="0" borderId="9" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="167" fillId="0" borderId="9" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="10" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="4" fillId="0" borderId="11" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="166" fillId="0" borderId="10" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="6" numFmtId="10" fillId="0" borderId="11" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="166" fillId="0" borderId="11" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="3" fillId="0" borderId="11" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="4" fillId="0" borderId="10" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="7" numFmtId="167" fillId="0" borderId="10" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="10" fillId="0" borderId="11" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="10" fillId="0" borderId="11" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="11" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="9" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="12" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" quotePrefix="1" numFmtId="168" fillId="0" borderId="3" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="13" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="14" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="165" fillId="0" borderId="10" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" quotePrefix="1" numFmtId="171" fillId="0" borderId="12" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="3" fillId="0" borderId="12" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="9" fillId="0" borderId="12" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="9" numFmtId="166" fillId="0" borderId="3" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="10" fillId="0" borderId="3" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="10" fillId="0" borderId="5" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="10" fillId="2" borderId="5" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="10" fillId="2" borderId="9" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="10" numFmtId="166" fillId="0" borderId="10" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="2" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="3" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="11" numFmtId="10" fillId="0" borderId="3" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="166" fillId="0" borderId="3" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="12" numFmtId="0" fillId="2" borderId="15" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="12" numFmtId="0" fillId="2" borderId="16" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="12" numFmtId="0" fillId="2" borderId="17" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="13" numFmtId="0" fillId="2" borderId="18" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="13" numFmtId="0" fillId="2" borderId="19" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="13" numFmtId="0" fillId="2" borderId="20" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="13" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="14" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="21" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="14" numFmtId="172" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="173" fillId="0" borderId="22" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="173" fillId="0" borderId="23" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="4" borderId="22" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="4" borderId="23" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="24" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="22" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="4" borderId="24" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="173" fillId="0" borderId="22" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="173" fillId="0" borderId="23" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="11">
-    <cellStyle name="Comma" xfId="3" builtinId="3"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Normal 2 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Normal 3" xfId="7" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="Normal 4" xfId="9" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Normal 5" xfId="4" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="Normale_GasProp" xfId="8" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
-    <cellStyle name="Percent 2" xfId="2" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="Percent 2 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
-    <cellStyle name="Percent 3" xfId="6" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -1127,7 +1081,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1179,7 +1133,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1231,7 +1185,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1240,164 +1194,192 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="Sheet1">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
     <tabColor rgb="FFFF0000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultColWidth="10.7265625" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr customHeight="true" defaultRowHeight="20.15" defaultColWidth="10.7265625" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="3" width="12.7265625" style="28" customWidth="1"/>
-    <col min="4" max="4" width="6.7265625" style="28" customWidth="1"/>
-    <col min="5" max="5" width="16.7265625" style="28" customWidth="1"/>
-    <col min="6" max="7" width="10.7265625" style="28"/>
-    <col min="8" max="8" width="22.7265625" style="28" customWidth="1"/>
-    <col min="9" max="9" width="14.7265625" style="28" customWidth="1"/>
-    <col min="10" max="16384" width="10.7265625" style="28"/>
+    <col min="1" max="1" width="12.7265625" customWidth="true" style="28"/>
+    <col min="2" max="2" width="12.7265625" customWidth="true" style="28"/>
+    <col min="3" max="3" width="12.7265625" customWidth="true" style="28"/>
+    <col min="4" max="4" width="6.7265625" customWidth="true" style="28"/>
+    <col min="5" max="5" width="16.7265625" customWidth="true" style="28"/>
+    <col min="6" max="6" width="10.7265625" style="28"/>
+    <col min="7" max="7" width="10.7265625" style="28"/>
+    <col min="8" max="8" width="22.7265625" customWidth="true" style="28"/>
+    <col min="9" max="9" width="14.7265625" customWidth="true" style="28"/>
+    <col min="10" max="10" width="10.7265625" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" customHeight="1" ht="20.15">
       <c r="A1" s="90" t="e">
         <f>"Biaya "&amp;DAY($I$1)&amp;" - "&amp;TEXT(EOMONTH($I$1,0),"[$-id-ID]d mmmm yyyy;@")</f>
         <v>#VALUE!</v>
@@ -1407,99 +1389,99 @@
       <c r="D1" s="90"/>
       <c r="E1" s="90"/>
       <c r="H1" s="54" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="I1" s="63" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" customHeight="1" ht="20.15">
       <c r="H2" s="54" t="s">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="I2" s="64">
         <v>1500000</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" customHeight="1" ht="20.15">
       <c r="A3" s="29"/>
       <c r="B3" s="29"/>
       <c r="C3" s="29"/>
       <c r="D3" s="29"/>
       <c r="E3" s="29"/>
       <c r="H3" s="54" t="s">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="I3" s="65">
         <v>0.25</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" customHeight="1" ht="20.15">
       <c r="A4" s="97" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B4" s="93"/>
       <c r="C4" s="93"/>
       <c r="D4" s="93" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E4" s="94"/>
     </row>
-    <row r="5" spans="1:9" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" customHeight="1" ht="20.15">
       <c r="A5" s="30" t="s">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="B5" s="31"/>
       <c r="C5" s="32"/>
       <c r="D5" s="98" t="s">
-        <v>57</v>
+        <v>7</v>
       </c>
       <c r="E5" s="99"/>
     </row>
-    <row r="6" spans="1:9" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" customHeight="1" ht="20.15">
       <c r="A6" s="95" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="96"/>
       <c r="C6" s="96"/>
       <c r="D6" s="91" t="s">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="E6" s="92"/>
     </row>
-    <row r="9" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" customHeight="1" ht="20.15">
       <c r="A9" s="28" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" customHeight="1" ht="20.15">
       <c r="A15" s="26" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="B15" s="34"/>
       <c r="C15" s="34"/>
       <c r="D15" s="26"/>
       <c r="E15" s="26" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" customHeight="1" ht="20.15">
       <c r="A16" s="27" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="B16" s="35"/>
       <c r="C16" s="35"/>
       <c r="D16" s="35"/>
       <c r="E16" s="27" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <mergeCells count="6">
+  <mergeCells>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="D4:E4"/>
@@ -1507,42 +1489,49 @@
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="D5:E5"/>
   </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="300" r:id="rId1"/>
+  <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true"/>
+  <pageMargins left="0.39370078740157" right="0.39370078740157" top="0.59055118110236" bottom="0.59055118110236" header="0.31496062992126" footer="0.31496062992126"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" r:id="rId1ps"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74EF875C-B333-4FE6-AE64-88669B17425F}">
-  <sheetPr codeName="Sheet4">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X37"/>
-  <sheetFormatPr defaultColWidth="12.7265625" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr customHeight="true" defaultRowHeight="20.15" defaultColWidth="12.7265625" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="11.7265625" style="22" customWidth="1"/>
-    <col min="2" max="2" width="10.7265625" style="22" hidden="1" customWidth="1"/>
-    <col min="3" max="4" width="10.7265625" style="22" customWidth="1"/>
-    <col min="5" max="5" width="12.7265625" style="22" customWidth="1"/>
-    <col min="6" max="6" width="10.7265625" style="22" customWidth="1"/>
-    <col min="7" max="7" width="12.7265625" style="22" customWidth="1"/>
-    <col min="8" max="9" width="10.7265625" style="22" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="12.7265625" style="22" hidden="1" customWidth="1"/>
-    <col min="11" max="13" width="9.7265625" style="22" customWidth="1"/>
-    <col min="14" max="14" width="10.7265625" style="22" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="12.7265625" style="22" customWidth="1"/>
-    <col min="16" max="18" width="10.7265625" style="22" customWidth="1"/>
-    <col min="19" max="19" width="18.453125" style="22" customWidth="1"/>
-    <col min="20" max="20" width="56.7265625" style="22" customWidth="1"/>
-    <col min="21" max="21" width="15.26953125" style="22" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="30.7265625" style="22" customWidth="1"/>
-    <col min="23" max="16384" width="12.7265625" style="22"/>
+    <col min="1" max="1" width="11.7265625" customWidth="true" style="22"/>
+    <col min="2" max="2" width="10.7265625" hidden="true" customWidth="true" style="22"/>
+    <col min="3" max="3" width="10.7265625" customWidth="true" style="22"/>
+    <col min="4" max="4" width="10.7265625" customWidth="true" style="22"/>
+    <col min="5" max="5" width="12.7265625" style="22"/>
+    <col min="6" max="6" width="10.7265625" customWidth="true" style="22"/>
+    <col min="7" max="7" width="12.7265625" style="22"/>
+    <col min="8" max="8" width="10.7265625" hidden="true" customWidth="true" style="22"/>
+    <col min="9" max="9" width="10.7265625" hidden="true" customWidth="true" style="22"/>
+    <col min="10" max="10" width="12.7265625" hidden="true" style="22"/>
+    <col min="11" max="11" width="9.7265625" customWidth="true" style="22"/>
+    <col min="12" max="12" width="9.7265625" customWidth="true" style="22"/>
+    <col min="13" max="13" width="9.7265625" customWidth="true" style="22"/>
+    <col min="14" max="14" width="10.7265625" hidden="true" customWidth="true" style="22"/>
+    <col min="15" max="15" width="12.7265625" style="22"/>
+    <col min="16" max="16" width="10.7265625" customWidth="true" style="22"/>
+    <col min="17" max="17" width="10.7265625" customWidth="true" style="22"/>
+    <col min="18" max="18" width="10.7265625" customWidth="true" style="22"/>
+    <col min="19" max="19" width="18.453125" customWidth="true" style="22"/>
+    <col min="20" max="20" width="56.7265625" customWidth="true" style="22"/>
+    <col min="21" max="21" width="15.26953125" customWidth="true" style="22"/>
+    <col min="22" max="22" width="30.7265625" customWidth="true" style="22"/>
+    <col min="23" max="23" width="12.7265625" style="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24" customHeight="1" ht="20.15">
       <c r="A1" s="79" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="B1" s="80"/>
       <c r="C1" s="80"/>
@@ -1568,9 +1557,9 @@
       <c r="W1" s="8"/>
       <c r="X1" s="9"/>
     </row>
-    <row r="2" spans="1:24" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:24" customHeight="1" ht="20.15">
       <c r="A2" s="82" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="B2" s="83"/>
       <c r="C2" s="83"/>
@@ -1593,7 +1582,7 @@
       <c r="T2" s="84"/>
       <c r="U2" s="9"/>
       <c r="V2" s="72" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="W2" s="33">
         <f>'Rekap Inv'!I2</f>
@@ -1601,14 +1590,14 @@
       </c>
       <c r="X2" s="9"/>
     </row>
-    <row r="3" spans="1:24" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:24" customHeight="1" ht="20.15">
       <c r="A3" s="1"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -1628,7 +1617,7 @@
       <c r="T3" s="5"/>
       <c r="U3" s="9"/>
       <c r="V3" s="73" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="W3" s="53">
         <f>'Rekap Inv'!I3</f>
@@ -1636,147 +1625,143 @@
       </c>
       <c r="X3" s="9"/>
     </row>
-    <row r="4" spans="1:24" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:24" customHeight="1" ht="20.15">
       <c r="A4" s="85" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K4" s="87" t="s">
-        <v>37</v>
-      </c>
-      <c r="L4" s="88" t="s">
-        <v>36</v>
-      </c>
-      <c r="M4" s="89" t="s">
-        <v>36</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="L4" s="88"/>
+      <c r="M4" s="89"/>
       <c r="N4" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="P4" s="87" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="Q4" s="88"/>
       <c r="R4" s="89"/>
       <c r="S4" s="56" t="s">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="T4" s="85" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="V4" s="73" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="W4" s="75">
         <v>0</v>
       </c>
       <c r="X4" s="22" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" customHeight="1" ht="20.15">
       <c r="A5" s="86"/>
       <c r="B5" s="7" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="C5" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="R5" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="S5" s="57" t="s">
         <v>48</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="O5" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P5" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q5" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="R5" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="S5" s="57" t="s">
-        <v>40</v>
       </c>
       <c r="T5" s="86"/>
       <c r="U5" s="76" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" ht="14.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" customHeight="1" ht="14.5">
       <c r="A6" s="55" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B6" s="12"/>
       <c r="C6" s="10" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F6" s="77">
         <f>IF(G6="","",IF(G6="BA",100%,E6/G6))</f>
@@ -1792,17 +1777,15 @@
       <c r="I6" s="13">
         <v>1845</v>
       </c>
-      <c r="J6" s="12" t="s">
-        <v>36</v>
-      </c>
+      <c r="J6" s="12"/>
       <c r="K6" s="19" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L6" s="19" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M6" s="19" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N6" s="67">
         <v>1</v>
@@ -1816,11 +1799,11 @@
         <v>#VALUE!</v>
       </c>
       <c r="Q6" s="66" t="e">
-        <f t="shared" ref="Q6:R21" si="0">IF(L6="","",L6*24)</f>
+        <f>IF(L6="","",L6*24)</f>
         <v>#VALUE!</v>
       </c>
       <c r="R6" s="66" t="e">
-        <f t="shared" si="0"/>
+        <f>IF(M6="","",M6*24)</f>
         <v>#VALUE!</v>
       </c>
       <c r="S6" s="25" t="e">
@@ -1828,26 +1811,26 @@
         <v>#VALUE!</v>
       </c>
       <c r="T6" s="58" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="U6" s="74" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="V6" s="23"/>
       <c r="W6" s="24"/>
     </row>
-    <row r="7" spans="1:24" ht="14.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:24" customHeight="1" ht="14.5">
       <c r="A7" s="20"/>
       <c r="B7" s="17"/>
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
       <c r="E7" s="16"/>
       <c r="F7" s="77">
-        <f t="shared" ref="F7:F36" si="1">IF(G7="","",IF(G7="BA",100%,E7/G7))</f>
+        <f>IF(G7="","",IF(G7="BA",100%,E7/G7))</f>
         <v>1</v>
       </c>
       <c r="G7" s="78" t="str">
-        <f t="shared" ref="G7:G36" si="2">IF(U7="","",IF(U7="BA","BA",U7))</f>
+        <f>IF(U7="","",IF(U7="BA","BA",U7))</f>
         <v>BA</v>
       </c>
       <c r="H7" s="17"/>
@@ -1858,44 +1841,44 @@
       <c r="M7" s="14"/>
       <c r="N7" s="68"/>
       <c r="O7" s="21" t="str">
-        <f t="shared" ref="O7" si="3">IF(OR($K7="",$L7="",$M7=""),"",($K7+$L7)/SUM($K7:$M7))</f>
+        <f>IF(OR($K7="",$L7="",$M7=""),"",($K7+$L7)/SUM($K7:$M7))</f>
         <v/>
       </c>
       <c r="P7" s="66" t="str">
-        <f t="shared" ref="P7:R36" si="4">IF(K7="","",K7*24)</f>
+        <f>IF(K7="","",K7*24)</f>
         <v/>
       </c>
       <c r="Q7" s="66" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(L7="","",L7*24)</f>
         <v/>
       </c>
       <c r="R7" s="66" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="S7" s="25">
+        <f>IF(M7="","",M7*24)</f>
+        <v/>
+      </c>
+      <c r="S7" s="25" t="e">
         <f>IF(R7&gt;(24-6),0,IF((AND(P7=0,(COUNTIF(Q$6:Q7,24)+$W$4)&gt;10)),0,IF(U7="BA",(100%*P7+$W$3*Q7)/24*$W$2,(F7*P7+$W$3*Q7)/24*$W$2)))</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="T7" s="59"/>
       <c r="U7" s="74" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="V7" s="23"/>
       <c r="W7" s="24"/>
     </row>
-    <row r="8" spans="1:24" ht="14.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:24" customHeight="1" ht="14.5">
       <c r="A8" s="20"/>
       <c r="B8" s="17"/>
       <c r="C8" s="15"/>
       <c r="D8" s="15"/>
       <c r="E8" s="16"/>
       <c r="F8" s="77">
-        <f t="shared" si="1"/>
+        <f>IF(G8="","",IF(G8="BA",100%,E8/G8))</f>
         <v>1</v>
       </c>
       <c r="G8" s="78" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(U8="","",IF(U8="BA","BA",U8))</f>
         <v>BA</v>
       </c>
       <c r="H8" s="17"/>
@@ -1906,44 +1889,44 @@
       <c r="M8" s="14"/>
       <c r="N8" s="68"/>
       <c r="O8" s="21" t="str">
-        <f t="shared" ref="O8:O36" si="5">IF(OR($K8="",$L8="",$M8=""),"",($K8+$L8)/SUM($K8:$M8))</f>
+        <f>IF(OR($K8="",$L8="",$M8=""),"",($K8+$L8)/SUM($K8:$M8))</f>
         <v/>
       </c>
       <c r="P8" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(K8="","",K8*24)</f>
         <v/>
       </c>
       <c r="Q8" s="66" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(L8="","",L8*24)</f>
         <v/>
       </c>
       <c r="R8" s="66" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="S8" s="25">
+        <f>IF(M8="","",M8*24)</f>
+        <v/>
+      </c>
+      <c r="S8" s="25" t="e">
         <f>IF(R8&gt;(24-6),0,IF((AND(P8=0,(COUNTIF(Q$6:Q8,24)+$W$4)&gt;10)),0,IF(U8="BA",(100%*P8+$W$3*Q8)/24*$W$2,(F8*P8+$W$3*Q8)/24*$W$2)))</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="T8" s="59"/>
       <c r="U8" s="74" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="V8" s="23"/>
       <c r="W8" s="24"/>
     </row>
-    <row r="9" spans="1:24" ht="14.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:24" customHeight="1" ht="14.5">
       <c r="A9" s="20"/>
       <c r="B9" s="17"/>
       <c r="C9" s="15"/>
       <c r="D9" s="15"/>
       <c r="E9" s="16"/>
       <c r="F9" s="77">
-        <f t="shared" si="1"/>
+        <f>IF(G9="","",IF(G9="BA",100%,E9/G9))</f>
         <v>1</v>
       </c>
       <c r="G9" s="78" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(U9="","",IF(U9="BA","BA",U9))</f>
         <v>BA</v>
       </c>
       <c r="H9" s="17"/>
@@ -1954,44 +1937,44 @@
       <c r="M9" s="14"/>
       <c r="N9" s="68"/>
       <c r="O9" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(OR($K9="",$L9="",$M9=""),"",($K9+$L9)/SUM($K9:$M9))</f>
         <v/>
       </c>
       <c r="P9" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(K9="","",K9*24)</f>
         <v/>
       </c>
       <c r="Q9" s="66" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(L9="","",L9*24)</f>
         <v/>
       </c>
       <c r="R9" s="66" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="S9" s="25">
+        <f>IF(M9="","",M9*24)</f>
+        <v/>
+      </c>
+      <c r="S9" s="25" t="e">
         <f>IF(R9&gt;(24-6),0,IF((AND(P9=0,(COUNTIF(Q$6:Q9,24)+$W$4)&gt;10)),0,IF(U9="BA",(100%*P9+$W$3*Q9)/24*$W$2,(F9*P9+$W$3*Q9)/24*$W$2)))</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="T9" s="59"/>
       <c r="U9" s="74" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="V9" s="23"/>
       <c r="W9" s="24"/>
     </row>
-    <row r="10" spans="1:24" ht="14.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:24" customHeight="1" ht="14.5">
       <c r="A10" s="20"/>
       <c r="B10" s="17"/>
       <c r="C10" s="15"/>
       <c r="D10" s="15"/>
       <c r="E10" s="16"/>
       <c r="F10" s="77">
-        <f t="shared" si="1"/>
+        <f>IF(G10="","",IF(G10="BA",100%,E10/G10))</f>
         <v>1</v>
       </c>
       <c r="G10" s="78" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(U10="","",IF(U10="BA","BA",U10))</f>
         <v>BA</v>
       </c>
       <c r="H10" s="17"/>
@@ -2002,44 +1985,44 @@
       <c r="M10" s="14"/>
       <c r="N10" s="68"/>
       <c r="O10" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(OR($K10="",$L10="",$M10=""),"",($K10+$L10)/SUM($K10:$M10))</f>
         <v/>
       </c>
       <c r="P10" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(K10="","",K10*24)</f>
         <v/>
       </c>
       <c r="Q10" s="66" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(L10="","",L10*24)</f>
         <v/>
       </c>
       <c r="R10" s="66" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="S10" s="25">
+        <f>IF(M10="","",M10*24)</f>
+        <v/>
+      </c>
+      <c r="S10" s="25" t="e">
         <f>IF(R10&gt;(24-6),0,IF((AND(P10=0,(COUNTIF(Q$6:Q10,24)+$W$4)&gt;10)),0,IF(U10="BA",(100%*P10+$W$3*Q10)/24*$W$2,(F10*P10+$W$3*Q10)/24*$W$2)))</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="T10" s="59"/>
       <c r="U10" s="74" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="V10" s="23"/>
       <c r="W10" s="24"/>
     </row>
-    <row r="11" spans="1:24" ht="14.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:24" customHeight="1" ht="14.5">
       <c r="A11" s="20"/>
       <c r="B11" s="17"/>
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
       <c r="E11" s="16"/>
       <c r="F11" s="77">
-        <f t="shared" si="1"/>
+        <f>IF(G11="","",IF(G11="BA",100%,E11/G11))</f>
         <v>1</v>
       </c>
       <c r="G11" s="78" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(U11="","",IF(U11="BA","BA",U11))</f>
         <v>BA</v>
       </c>
       <c r="H11" s="17"/>
@@ -2050,44 +2033,44 @@
       <c r="M11" s="14"/>
       <c r="N11" s="68"/>
       <c r="O11" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(OR($K11="",$L11="",$M11=""),"",($K11+$L11)/SUM($K11:$M11))</f>
         <v/>
       </c>
       <c r="P11" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(K11="","",K11*24)</f>
         <v/>
       </c>
       <c r="Q11" s="66" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(L11="","",L11*24)</f>
         <v/>
       </c>
       <c r="R11" s="66" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="S11" s="25">
+        <f>IF(M11="","",M11*24)</f>
+        <v/>
+      </c>
+      <c r="S11" s="25" t="e">
         <f>IF(R11&gt;(24-6),0,IF((AND(P11=0,(COUNTIF(Q$6:Q11,24)+$W$4)&gt;10)),0,IF(U11="BA",(100%*P11+$W$3*Q11)/24*$W$2,(F11*P11+$W$3*Q11)/24*$W$2)))</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="T11" s="59"/>
       <c r="U11" s="74" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="V11" s="23"/>
       <c r="W11" s="24"/>
     </row>
-    <row r="12" spans="1:24" ht="14.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:24" customHeight="1" ht="14.5">
       <c r="A12" s="20"/>
       <c r="B12" s="17"/>
       <c r="C12" s="15"/>
       <c r="D12" s="15"/>
       <c r="E12" s="16"/>
       <c r="F12" s="77">
-        <f t="shared" si="1"/>
+        <f>IF(G12="","",IF(G12="BA",100%,E12/G12))</f>
         <v>1</v>
       </c>
       <c r="G12" s="78" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(U12="","",IF(U12="BA","BA",U12))</f>
         <v>BA</v>
       </c>
       <c r="H12" s="17"/>
@@ -2098,44 +2081,44 @@
       <c r="M12" s="14"/>
       <c r="N12" s="68"/>
       <c r="O12" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(OR($K12="",$L12="",$M12=""),"",($K12+$L12)/SUM($K12:$M12))</f>
         <v/>
       </c>
       <c r="P12" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(K12="","",K12*24)</f>
         <v/>
       </c>
       <c r="Q12" s="66" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(L12="","",L12*24)</f>
         <v/>
       </c>
       <c r="R12" s="66" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="S12" s="25">
+        <f>IF(M12="","",M12*24)</f>
+        <v/>
+      </c>
+      <c r="S12" s="25" t="e">
         <f>IF(R12&gt;(24-6),0,IF((AND(P12=0,(COUNTIF(Q$6:Q12,24)+$W$4)&gt;10)),0,IF(U12="BA",(100%*P12+$W$3*Q12)/24*$W$2,(F12*P12+$W$3*Q12)/24*$W$2)))</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="T12" s="59"/>
       <c r="U12" s="74" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="V12" s="23"/>
       <c r="W12" s="24"/>
     </row>
-    <row r="13" spans="1:24" ht="14.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:24" customHeight="1" ht="14.5">
       <c r="A13" s="20"/>
       <c r="B13" s="17"/>
       <c r="C13" s="15"/>
       <c r="D13" s="15"/>
       <c r="E13" s="16"/>
       <c r="F13" s="77">
-        <f t="shared" si="1"/>
+        <f>IF(G13="","",IF(G13="BA",100%,E13/G13))</f>
         <v>1</v>
       </c>
       <c r="G13" s="78" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(U13="","",IF(U13="BA","BA",U13))</f>
         <v>BA</v>
       </c>
       <c r="H13" s="17"/>
@@ -2146,44 +2129,44 @@
       <c r="M13" s="14"/>
       <c r="N13" s="68"/>
       <c r="O13" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(OR($K13="",$L13="",$M13=""),"",($K13+$L13)/SUM($K13:$M13))</f>
         <v/>
       </c>
       <c r="P13" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(K13="","",K13*24)</f>
         <v/>
       </c>
       <c r="Q13" s="66" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(L13="","",L13*24)</f>
         <v/>
       </c>
       <c r="R13" s="66" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="S13" s="25">
+        <f>IF(M13="","",M13*24)</f>
+        <v/>
+      </c>
+      <c r="S13" s="25" t="e">
         <f>IF(R13&gt;(24-6),0,IF((AND(P13=0,(COUNTIF(Q$6:Q13,24)+$W$4)&gt;10)),0,IF(U13="BA",(100%*P13+$W$3*Q13)/24*$W$2,(F13*P13+$W$3*Q13)/24*$W$2)))</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="T13" s="59"/>
       <c r="U13" s="74" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="V13" s="23"/>
       <c r="W13" s="24"/>
     </row>
-    <row r="14" spans="1:24" ht="14.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:24" customHeight="1" ht="14.5">
       <c r="A14" s="20"/>
       <c r="B14" s="17"/>
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
       <c r="E14" s="16"/>
       <c r="F14" s="77">
-        <f t="shared" si="1"/>
+        <f>IF(G14="","",IF(G14="BA",100%,E14/G14))</f>
         <v>1</v>
       </c>
       <c r="G14" s="78" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(U14="","",IF(U14="BA","BA",U14))</f>
         <v>BA</v>
       </c>
       <c r="H14" s="17"/>
@@ -2194,44 +2177,44 @@
       <c r="M14" s="14"/>
       <c r="N14" s="68"/>
       <c r="O14" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(OR($K14="",$L14="",$M14=""),"",($K14+$L14)/SUM($K14:$M14))</f>
         <v/>
       </c>
       <c r="P14" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(K14="","",K14*24)</f>
         <v/>
       </c>
       <c r="Q14" s="66" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(L14="","",L14*24)</f>
         <v/>
       </c>
       <c r="R14" s="66" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="S14" s="25">
+        <f>IF(M14="","",M14*24)</f>
+        <v/>
+      </c>
+      <c r="S14" s="25" t="e">
         <f>IF(R14&gt;(24-6),0,IF((AND(P14=0,(COUNTIF(Q$6:Q14,24)+$W$4)&gt;10)),0,IF(U14="BA",(100%*P14+$W$3*Q14)/24*$W$2,(F14*P14+$W$3*Q14)/24*$W$2)))</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="T14" s="59"/>
       <c r="U14" s="74" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="V14" s="23"/>
       <c r="W14" s="24"/>
     </row>
-    <row r="15" spans="1:24" ht="14.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:24" customHeight="1" ht="14.5">
       <c r="A15" s="20"/>
       <c r="B15" s="17"/>
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
       <c r="E15" s="16"/>
       <c r="F15" s="77">
-        <f t="shared" si="1"/>
+        <f>IF(G15="","",IF(G15="BA",100%,E15/G15))</f>
         <v>1</v>
       </c>
       <c r="G15" s="78" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(U15="","",IF(U15="BA","BA",U15))</f>
         <v>BA</v>
       </c>
       <c r="H15" s="17"/>
@@ -2242,44 +2225,44 @@
       <c r="M15" s="14"/>
       <c r="N15" s="68"/>
       <c r="O15" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(OR($K15="",$L15="",$M15=""),"",($K15+$L15)/SUM($K15:$M15))</f>
         <v/>
       </c>
       <c r="P15" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(K15="","",K15*24)</f>
         <v/>
       </c>
       <c r="Q15" s="66" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(L15="","",L15*24)</f>
         <v/>
       </c>
       <c r="R15" s="66" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="S15" s="25">
+        <f>IF(M15="","",M15*24)</f>
+        <v/>
+      </c>
+      <c r="S15" s="25" t="e">
         <f>IF(R15&gt;(24-6),0,IF((AND(P15=0,(COUNTIF(Q$6:Q15,24)+$W$4)&gt;10)),0,IF(U15="BA",(100%*P15+$W$3*Q15)/24*$W$2,(F15*P15+$W$3*Q15)/24*$W$2)))</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="T15" s="59"/>
       <c r="U15" s="74" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="V15" s="23"/>
       <c r="W15" s="24"/>
     </row>
-    <row r="16" spans="1:24" ht="14.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:24" customHeight="1" ht="14.5">
       <c r="A16" s="20"/>
       <c r="B16" s="17"/>
       <c r="C16" s="15"/>
       <c r="D16" s="15"/>
       <c r="E16" s="16"/>
       <c r="F16" s="77">
-        <f t="shared" si="1"/>
+        <f>IF(G16="","",IF(G16="BA",100%,E16/G16))</f>
         <v>1</v>
       </c>
       <c r="G16" s="78" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(U16="","",IF(U16="BA","BA",U16))</f>
         <v>BA</v>
       </c>
       <c r="H16" s="17"/>
@@ -2290,44 +2273,44 @@
       <c r="M16" s="14"/>
       <c r="N16" s="68"/>
       <c r="O16" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(OR($K16="",$L16="",$M16=""),"",($K16+$L16)/SUM($K16:$M16))</f>
         <v/>
       </c>
       <c r="P16" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(K16="","",K16*24)</f>
         <v/>
       </c>
       <c r="Q16" s="66" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(L16="","",L16*24)</f>
         <v/>
       </c>
       <c r="R16" s="66" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="S16" s="25">
+        <f>IF(M16="","",M16*24)</f>
+        <v/>
+      </c>
+      <c r="S16" s="25" t="e">
         <f>IF(R16&gt;(24-6),0,IF((AND(P16=0,(COUNTIF(Q$6:Q16,24)+$W$4)&gt;10)),0,IF(U16="BA",(100%*P16+$W$3*Q16)/24*$W$2,(F16*P16+$W$3*Q16)/24*$W$2)))</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="T16" s="59"/>
       <c r="U16" s="74" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="V16" s="23"/>
       <c r="W16" s="24"/>
     </row>
-    <row r="17" spans="1:23" ht="14.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:24" customHeight="1" ht="14.5">
       <c r="A17" s="20"/>
       <c r="B17" s="17"/>
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
       <c r="E17" s="16"/>
       <c r="F17" s="77">
-        <f t="shared" si="1"/>
+        <f>IF(G17="","",IF(G17="BA",100%,E17/G17))</f>
         <v>1</v>
       </c>
       <c r="G17" s="78" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(U17="","",IF(U17="BA","BA",U17))</f>
         <v>BA</v>
       </c>
       <c r="H17" s="17"/>
@@ -2338,44 +2321,44 @@
       <c r="M17" s="14"/>
       <c r="N17" s="68"/>
       <c r="O17" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(OR($K17="",$L17="",$M17=""),"",($K17+$L17)/SUM($K17:$M17))</f>
         <v/>
       </c>
       <c r="P17" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(K17="","",K17*24)</f>
         <v/>
       </c>
       <c r="Q17" s="66" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(L17="","",L17*24)</f>
         <v/>
       </c>
       <c r="R17" s="66" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="S17" s="25">
+        <f>IF(M17="","",M17*24)</f>
+        <v/>
+      </c>
+      <c r="S17" s="25" t="e">
         <f>IF(R17&gt;(24-6),0,IF((AND(P17=0,(COUNTIF(Q$6:Q17,24)+$W$4)&gt;10)),0,IF(U17="BA",(100%*P17+$W$3*Q17)/24*$W$2,(F17*P17+$W$3*Q17)/24*$W$2)))</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="T17" s="59"/>
       <c r="U17" s="74" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="V17" s="23"/>
       <c r="W17" s="24"/>
     </row>
-    <row r="18" spans="1:23" ht="14.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:24" customHeight="1" ht="14.5">
       <c r="A18" s="20"/>
       <c r="B18" s="17"/>
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
       <c r="E18" s="16"/>
       <c r="F18" s="77">
-        <f t="shared" si="1"/>
+        <f>IF(G18="","",IF(G18="BA",100%,E18/G18))</f>
         <v>1</v>
       </c>
       <c r="G18" s="78" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(U18="","",IF(U18="BA","BA",U18))</f>
         <v>BA</v>
       </c>
       <c r="H18" s="17"/>
@@ -2386,44 +2369,44 @@
       <c r="M18" s="14"/>
       <c r="N18" s="68"/>
       <c r="O18" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(OR($K18="",$L18="",$M18=""),"",($K18+$L18)/SUM($K18:$M18))</f>
         <v/>
       </c>
       <c r="P18" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(K18="","",K18*24)</f>
         <v/>
       </c>
       <c r="Q18" s="66" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(L18="","",L18*24)</f>
         <v/>
       </c>
       <c r="R18" s="66" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="S18" s="25">
+        <f>IF(M18="","",M18*24)</f>
+        <v/>
+      </c>
+      <c r="S18" s="25" t="e">
         <f>IF(R18&gt;(24-6),0,IF((AND(P18=0,(COUNTIF(Q$6:Q18,24)+$W$4)&gt;10)),0,IF(U18="BA",(100%*P18+$W$3*Q18)/24*$W$2,(F18*P18+$W$3*Q18)/24*$W$2)))</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="T18" s="59"/>
       <c r="U18" s="74" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="V18" s="23"/>
       <c r="W18" s="24"/>
     </row>
-    <row r="19" spans="1:23" ht="14.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:24" customHeight="1" ht="14.5">
       <c r="A19" s="20"/>
       <c r="B19" s="17"/>
       <c r="C19" s="15"/>
       <c r="D19" s="15"/>
       <c r="E19" s="16"/>
       <c r="F19" s="77">
-        <f t="shared" si="1"/>
+        <f>IF(G19="","",IF(G19="BA",100%,E19/G19))</f>
         <v>1</v>
       </c>
       <c r="G19" s="78" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(U19="","",IF(U19="BA","BA",U19))</f>
         <v>BA</v>
       </c>
       <c r="H19" s="17"/>
@@ -2434,44 +2417,44 @@
       <c r="M19" s="14"/>
       <c r="N19" s="68"/>
       <c r="O19" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(OR($K19="",$L19="",$M19=""),"",($K19+$L19)/SUM($K19:$M19))</f>
         <v/>
       </c>
       <c r="P19" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(K19="","",K19*24)</f>
         <v/>
       </c>
       <c r="Q19" s="66" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(L19="","",L19*24)</f>
         <v/>
       </c>
       <c r="R19" s="66" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="S19" s="25">
+        <f>IF(M19="","",M19*24)</f>
+        <v/>
+      </c>
+      <c r="S19" s="25" t="e">
         <f>IF(R19&gt;(24-6),0,IF((AND(P19=0,(COUNTIF(Q$6:Q19,24)+$W$4)&gt;10)),0,IF(U19="BA",(100%*P19+$W$3*Q19)/24*$W$2,(F19*P19+$W$3*Q19)/24*$W$2)))</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="T19" s="59"/>
       <c r="U19" s="74" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="V19" s="23"/>
       <c r="W19" s="24"/>
     </row>
-    <row r="20" spans="1:23" ht="14.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:24" customHeight="1" ht="14.5">
       <c r="A20" s="20"/>
       <c r="B20" s="17"/>
       <c r="C20" s="15"/>
       <c r="D20" s="15"/>
       <c r="E20" s="16"/>
       <c r="F20" s="77">
-        <f t="shared" si="1"/>
+        <f>IF(G20="","",IF(G20="BA",100%,E20/G20))</f>
         <v>1</v>
       </c>
       <c r="G20" s="78" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(U20="","",IF(U20="BA","BA",U20))</f>
         <v>BA</v>
       </c>
       <c r="H20" s="17"/>
@@ -2482,44 +2465,44 @@
       <c r="M20" s="14"/>
       <c r="N20" s="68"/>
       <c r="O20" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(OR($K20="",$L20="",$M20=""),"",($K20+$L20)/SUM($K20:$M20))</f>
         <v/>
       </c>
       <c r="P20" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(K20="","",K20*24)</f>
         <v/>
       </c>
       <c r="Q20" s="66" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(L20="","",L20*24)</f>
         <v/>
       </c>
       <c r="R20" s="66" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="S20" s="25">
+        <f>IF(M20="","",M20*24)</f>
+        <v/>
+      </c>
+      <c r="S20" s="25" t="e">
         <f>IF(R20&gt;(24-6),0,IF((AND(P20=0,(COUNTIF(Q$6:Q20,24)+$W$4)&gt;10)),0,IF(U20="BA",(100%*P20+$W$3*Q20)/24*$W$2,(F20*P20+$W$3*Q20)/24*$W$2)))</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="T20" s="59"/>
       <c r="U20" s="74" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="V20" s="23"/>
       <c r="W20" s="24"/>
     </row>
-    <row r="21" spans="1:23" ht="14.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:24" customHeight="1" ht="14.5">
       <c r="A21" s="20"/>
       <c r="B21" s="17"/>
       <c r="C21" s="15"/>
       <c r="D21" s="15"/>
       <c r="E21" s="16"/>
       <c r="F21" s="77">
-        <f t="shared" si="1"/>
+        <f>IF(G21="","",IF(G21="BA",100%,E21/G21))</f>
         <v>1</v>
       </c>
       <c r="G21" s="78" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(U21="","",IF(U21="BA","BA",U21))</f>
         <v>BA</v>
       </c>
       <c r="H21" s="17"/>
@@ -2530,44 +2513,44 @@
       <c r="M21" s="14"/>
       <c r="N21" s="68"/>
       <c r="O21" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(OR($K21="",$L21="",$M21=""),"",($K21+$L21)/SUM($K21:$M21))</f>
         <v/>
       </c>
       <c r="P21" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(K21="","",K21*24)</f>
         <v/>
       </c>
       <c r="Q21" s="66" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(L21="","",L21*24)</f>
         <v/>
       </c>
       <c r="R21" s="66" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="S21" s="25">
+        <f>IF(M21="","",M21*24)</f>
+        <v/>
+      </c>
+      <c r="S21" s="25" t="e">
         <f>IF(R21&gt;(24-6),0,IF((AND(P21=0,(COUNTIF(Q$6:Q21,24)+$W$4)&gt;10)),0,IF(U21="BA",(100%*P21+$W$3*Q21)/24*$W$2,(F21*P21+$W$3*Q21)/24*$W$2)))</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="T21" s="59"/>
       <c r="U21" s="74" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="V21" s="23"/>
       <c r="W21" s="24"/>
     </row>
-    <row r="22" spans="1:23" ht="14.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:24" customHeight="1" ht="14.5">
       <c r="A22" s="20"/>
       <c r="B22" s="17"/>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
       <c r="E22" s="16"/>
       <c r="F22" s="77">
-        <f t="shared" si="1"/>
+        <f>IF(G22="","",IF(G22="BA",100%,E22/G22))</f>
         <v>1</v>
       </c>
       <c r="G22" s="78" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(U22="","",IF(U22="BA","BA",U22))</f>
         <v>BA</v>
       </c>
       <c r="H22" s="17"/>
@@ -2578,44 +2561,44 @@
       <c r="M22" s="14"/>
       <c r="N22" s="68"/>
       <c r="O22" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(OR($K22="",$L22="",$M22=""),"",($K22+$L22)/SUM($K22:$M22))</f>
         <v/>
       </c>
       <c r="P22" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(K22="","",K22*24)</f>
         <v/>
       </c>
       <c r="Q22" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(L22="","",L22*24)</f>
         <v/>
       </c>
       <c r="R22" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="S22" s="25">
+        <f>IF(M22="","",M22*24)</f>
+        <v/>
+      </c>
+      <c r="S22" s="25" t="e">
         <f>IF(R22&gt;(24-6),0,IF((AND(P22=0,(COUNTIF(Q$6:Q22,24)+$W$4)&gt;10)),0,IF(U22="BA",(100%*P22+$W$3*Q22)/24*$W$2,(F22*P22+$W$3*Q22)/24*$W$2)))</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="T22" s="59"/>
       <c r="U22" s="74" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="V22" s="23"/>
       <c r="W22" s="24"/>
     </row>
-    <row r="23" spans="1:23" ht="14.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:24" customHeight="1" ht="14.5">
       <c r="A23" s="20"/>
       <c r="B23" s="17"/>
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
       <c r="E23" s="16"/>
       <c r="F23" s="77">
-        <f t="shared" si="1"/>
+        <f>IF(G23="","",IF(G23="BA",100%,E23/G23))</f>
         <v>1</v>
       </c>
       <c r="G23" s="78" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(U23="","",IF(U23="BA","BA",U23))</f>
         <v>BA</v>
       </c>
       <c r="H23" s="17"/>
@@ -2626,44 +2609,44 @@
       <c r="M23" s="14"/>
       <c r="N23" s="68"/>
       <c r="O23" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(OR($K23="",$L23="",$M23=""),"",($K23+$L23)/SUM($K23:$M23))</f>
         <v/>
       </c>
       <c r="P23" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(K23="","",K23*24)</f>
         <v/>
       </c>
       <c r="Q23" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(L23="","",L23*24)</f>
         <v/>
       </c>
       <c r="R23" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="S23" s="25">
+        <f>IF(M23="","",M23*24)</f>
+        <v/>
+      </c>
+      <c r="S23" s="25" t="e">
         <f>IF(R23&gt;(24-6),0,IF((AND(P23=0,(COUNTIF(Q$6:Q23,24)+$W$4)&gt;10)),0,IF(U23="BA",(100%*P23+$W$3*Q23)/24*$W$2,(F23*P23+$W$3*Q23)/24*$W$2)))</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="T23" s="59"/>
       <c r="U23" s="74" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="V23" s="23"/>
       <c r="W23" s="24"/>
     </row>
-    <row r="24" spans="1:23" ht="14.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:24" customHeight="1" ht="14.5">
       <c r="A24" s="20"/>
       <c r="B24" s="17"/>
       <c r="C24" s="15"/>
       <c r="D24" s="15"/>
       <c r="E24" s="16"/>
       <c r="F24" s="77">
-        <f t="shared" si="1"/>
+        <f>IF(G24="","",IF(G24="BA",100%,E24/G24))</f>
         <v>1</v>
       </c>
       <c r="G24" s="78" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(U24="","",IF(U24="BA","BA",U24))</f>
         <v>BA</v>
       </c>
       <c r="H24" s="17"/>
@@ -2674,44 +2657,44 @@
       <c r="M24" s="14"/>
       <c r="N24" s="68"/>
       <c r="O24" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(OR($K24="",$L24="",$M24=""),"",($K24+$L24)/SUM($K24:$M24))</f>
         <v/>
       </c>
       <c r="P24" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(K24="","",K24*24)</f>
         <v/>
       </c>
       <c r="Q24" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(L24="","",L24*24)</f>
         <v/>
       </c>
       <c r="R24" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="S24" s="25">
+        <f>IF(M24="","",M24*24)</f>
+        <v/>
+      </c>
+      <c r="S24" s="25" t="e">
         <f>IF(R24&gt;(24-6),0,IF((AND(P24=0,(COUNTIF(Q$6:Q24,24)+$W$4)&gt;10)),0,IF(U24="BA",(100%*P24+$W$3*Q24)/24*$W$2,(F24*P24+$W$3*Q24)/24*$W$2)))</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="T24" s="59"/>
       <c r="U24" s="74" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="V24" s="23"/>
       <c r="W24" s="24"/>
     </row>
-    <row r="25" spans="1:23" ht="14.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:24" customHeight="1" ht="14.5">
       <c r="A25" s="20"/>
       <c r="B25" s="17"/>
       <c r="C25" s="15"/>
       <c r="D25" s="15"/>
       <c r="E25" s="16"/>
       <c r="F25" s="77">
-        <f t="shared" si="1"/>
+        <f>IF(G25="","",IF(G25="BA",100%,E25/G25))</f>
         <v>1</v>
       </c>
       <c r="G25" s="78" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(U25="","",IF(U25="BA","BA",U25))</f>
         <v>BA</v>
       </c>
       <c r="H25" s="17"/>
@@ -2722,44 +2705,44 @@
       <c r="M25" s="14"/>
       <c r="N25" s="68"/>
       <c r="O25" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(OR($K25="",$L25="",$M25=""),"",($K25+$L25)/SUM($K25:$M25))</f>
         <v/>
       </c>
       <c r="P25" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(K25="","",K25*24)</f>
         <v/>
       </c>
       <c r="Q25" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(L25="","",L25*24)</f>
         <v/>
       </c>
       <c r="R25" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="S25" s="25">
+        <f>IF(M25="","",M25*24)</f>
+        <v/>
+      </c>
+      <c r="S25" s="25" t="e">
         <f>IF(R25&gt;(24-6),0,IF((AND(P25=0,(COUNTIF(Q$6:Q25,24)+$W$4)&gt;10)),0,IF(U25="BA",(100%*P25+$W$3*Q25)/24*$W$2,(F25*P25+$W$3*Q25)/24*$W$2)))</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="T25" s="59"/>
       <c r="U25" s="74" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="V25" s="23"/>
       <c r="W25" s="24"/>
     </row>
-    <row r="26" spans="1:23" ht="14.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:24" customHeight="1" ht="14.5">
       <c r="A26" s="20"/>
       <c r="B26" s="17"/>
       <c r="C26" s="15"/>
       <c r="D26" s="15"/>
       <c r="E26" s="16"/>
       <c r="F26" s="77">
-        <f t="shared" si="1"/>
+        <f>IF(G26="","",IF(G26="BA",100%,E26/G26))</f>
         <v>1</v>
       </c>
       <c r="G26" s="78" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(U26="","",IF(U26="BA","BA",U26))</f>
         <v>BA</v>
       </c>
       <c r="H26" s="17"/>
@@ -2770,44 +2753,44 @@
       <c r="M26" s="14"/>
       <c r="N26" s="69"/>
       <c r="O26" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(OR($K26="",$L26="",$M26=""),"",($K26+$L26)/SUM($K26:$M26))</f>
         <v/>
       </c>
       <c r="P26" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(K26="","",K26*24)</f>
         <v/>
       </c>
       <c r="Q26" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(L26="","",L26*24)</f>
         <v/>
       </c>
       <c r="R26" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="S26" s="25">
+        <f>IF(M26="","",M26*24)</f>
+        <v/>
+      </c>
+      <c r="S26" s="25" t="e">
         <f>IF(R26&gt;(24-6),0,IF((AND(P26=0,(COUNTIF(Q$6:Q26,24)+$W$4)&gt;10)),0,IF(U26="BA",(100%*P26+$W$3*Q26)/24*$W$2,(F26*P26+$W$3*Q26)/24*$W$2)))</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="T26" s="59"/>
       <c r="U26" s="74" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="V26" s="23"/>
       <c r="W26" s="24"/>
     </row>
-    <row r="27" spans="1:23" ht="14.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:24" customHeight="1" ht="14.5">
       <c r="A27" s="20"/>
       <c r="B27" s="17"/>
       <c r="C27" s="15"/>
       <c r="D27" s="15"/>
       <c r="E27" s="16"/>
       <c r="F27" s="77">
-        <f t="shared" si="1"/>
+        <f>IF(G27="","",IF(G27="BA",100%,E27/G27))</f>
         <v>1</v>
       </c>
       <c r="G27" s="78" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(U27="","",IF(U27="BA","BA",U27))</f>
         <v>BA</v>
       </c>
       <c r="H27" s="17"/>
@@ -2818,44 +2801,44 @@
       <c r="M27" s="14"/>
       <c r="N27" s="69"/>
       <c r="O27" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(OR($K27="",$L27="",$M27=""),"",($K27+$L27)/SUM($K27:$M27))</f>
         <v/>
       </c>
       <c r="P27" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(K27="","",K27*24)</f>
         <v/>
       </c>
       <c r="Q27" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(L27="","",L27*24)</f>
         <v/>
       </c>
       <c r="R27" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="S27" s="25">
+        <f>IF(M27="","",M27*24)</f>
+        <v/>
+      </c>
+      <c r="S27" s="25" t="e">
         <f>IF(R27&gt;(24-6),0,IF((AND(P27=0,(COUNTIF(Q$6:Q27,24)+$W$4)&gt;10)),0,IF(U27="BA",(100%*P27+$W$3*Q27)/24*$W$2,(F27*P27+$W$3*Q27)/24*$W$2)))</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="T27" s="59"/>
       <c r="U27" s="74" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="V27" s="23"/>
       <c r="W27" s="24"/>
     </row>
-    <row r="28" spans="1:23" ht="14.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:24" customHeight="1" ht="14.5">
       <c r="A28" s="20"/>
       <c r="B28" s="17"/>
       <c r="C28" s="15"/>
       <c r="D28" s="15"/>
       <c r="E28" s="16"/>
       <c r="F28" s="77">
-        <f t="shared" si="1"/>
+        <f>IF(G28="","",IF(G28="BA",100%,E28/G28))</f>
         <v>1</v>
       </c>
       <c r="G28" s="78" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(U28="","",IF(U28="BA","BA",U28))</f>
         <v>BA</v>
       </c>
       <c r="H28" s="17"/>
@@ -2866,44 +2849,44 @@
       <c r="M28" s="14"/>
       <c r="N28" s="69"/>
       <c r="O28" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(OR($K28="",$L28="",$M28=""),"",($K28+$L28)/SUM($K28:$M28))</f>
         <v/>
       </c>
       <c r="P28" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(K28="","",K28*24)</f>
         <v/>
       </c>
       <c r="Q28" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(L28="","",L28*24)</f>
         <v/>
       </c>
       <c r="R28" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="S28" s="25">
+        <f>IF(M28="","",M28*24)</f>
+        <v/>
+      </c>
+      <c r="S28" s="25" t="e">
         <f>IF(R28&gt;(24-6),0,IF((AND(P28=0,(COUNTIF(Q$6:Q28,24)+$W$4)&gt;10)),0,IF(U28="BA",(100%*P28+$W$3*Q28)/24*$W$2,(F28*P28+$W$3*Q28)/24*$W$2)))</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="T28" s="59"/>
       <c r="U28" s="74" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="V28" s="23"/>
       <c r="W28" s="24"/>
     </row>
-    <row r="29" spans="1:23" ht="14.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:24" customHeight="1" ht="14.5">
       <c r="A29" s="20"/>
       <c r="B29" s="17"/>
       <c r="C29" s="15"/>
       <c r="D29" s="15"/>
       <c r="E29" s="16"/>
       <c r="F29" s="77">
-        <f t="shared" si="1"/>
+        <f>IF(G29="","",IF(G29="BA",100%,E29/G29))</f>
         <v>1</v>
       </c>
       <c r="G29" s="78" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(U29="","",IF(U29="BA","BA",U29))</f>
         <v>BA</v>
       </c>
       <c r="H29" s="17"/>
@@ -2914,44 +2897,44 @@
       <c r="M29" s="14"/>
       <c r="N29" s="69"/>
       <c r="O29" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(OR($K29="",$L29="",$M29=""),"",($K29+$L29)/SUM($K29:$M29))</f>
         <v/>
       </c>
       <c r="P29" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(K29="","",K29*24)</f>
         <v/>
       </c>
       <c r="Q29" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(L29="","",L29*24)</f>
         <v/>
       </c>
       <c r="R29" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="S29" s="25">
+        <f>IF(M29="","",M29*24)</f>
+        <v/>
+      </c>
+      <c r="S29" s="25" t="e">
         <f>IF(R29&gt;(24-6),0,IF((AND(P29=0,(COUNTIF(Q$6:Q29,24)+$W$4)&gt;10)),0,IF(U29="BA",(100%*P29+$W$3*Q29)/24*$W$2,(F29*P29+$W$3*Q29)/24*$W$2)))</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="T29" s="59"/>
       <c r="U29" s="74" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="V29" s="23"/>
       <c r="W29" s="24"/>
     </row>
-    <row r="30" spans="1:23" ht="14.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:24" customHeight="1" ht="14.5">
       <c r="A30" s="20"/>
       <c r="B30" s="17"/>
       <c r="C30" s="15"/>
       <c r="D30" s="15"/>
       <c r="E30" s="16"/>
       <c r="F30" s="77">
-        <f t="shared" si="1"/>
+        <f>IF(G30="","",IF(G30="BA",100%,E30/G30))</f>
         <v>1</v>
       </c>
       <c r="G30" s="78" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(U30="","",IF(U30="BA","BA",U30))</f>
         <v>BA</v>
       </c>
       <c r="H30" s="17"/>
@@ -2962,44 +2945,44 @@
       <c r="M30" s="14"/>
       <c r="N30" s="69"/>
       <c r="O30" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(OR($K30="",$L30="",$M30=""),"",($K30+$L30)/SUM($K30:$M30))</f>
         <v/>
       </c>
       <c r="P30" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(K30="","",K30*24)</f>
         <v/>
       </c>
       <c r="Q30" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(L30="","",L30*24)</f>
         <v/>
       </c>
       <c r="R30" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="S30" s="25">
+        <f>IF(M30="","",M30*24)</f>
+        <v/>
+      </c>
+      <c r="S30" s="25" t="e">
         <f>IF(R30&gt;(24-6),0,IF((AND(P30=0,(COUNTIF(Q$6:Q30,24)+$W$4)&gt;10)),0,IF(U30="BA",(100%*P30+$W$3*Q30)/24*$W$2,(F30*P30+$W$3*Q30)/24*$W$2)))</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="T30" s="60"/>
       <c r="U30" s="74" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="V30" s="23"/>
       <c r="W30" s="24"/>
     </row>
-    <row r="31" spans="1:23" ht="14.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:24" customHeight="1" ht="14.5">
       <c r="A31" s="20"/>
       <c r="B31" s="17"/>
       <c r="C31" s="15"/>
       <c r="D31" s="15"/>
       <c r="E31" s="16"/>
       <c r="F31" s="77">
-        <f t="shared" si="1"/>
+        <f>IF(G31="","",IF(G31="BA",100%,E31/G31))</f>
         <v>1</v>
       </c>
       <c r="G31" s="78" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(U31="","",IF(U31="BA","BA",U31))</f>
         <v>BA</v>
       </c>
       <c r="H31" s="17"/>
@@ -3010,44 +2993,44 @@
       <c r="M31" s="14"/>
       <c r="N31" s="69"/>
       <c r="O31" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(OR($K31="",$L31="",$M31=""),"",($K31+$L31)/SUM($K31:$M31))</f>
         <v/>
       </c>
       <c r="P31" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(K31="","",K31*24)</f>
         <v/>
       </c>
       <c r="Q31" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(L31="","",L31*24)</f>
         <v/>
       </c>
       <c r="R31" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="S31" s="25">
+        <f>IF(M31="","",M31*24)</f>
+        <v/>
+      </c>
+      <c r="S31" s="25" t="e">
         <f>IF(R31&gt;(24-6),0,IF((AND(P31=0,(COUNTIF(Q$6:Q31,24)+$W$4)&gt;10)),0,IF(U31="BA",(100%*P31+$W$3*Q31)/24*$W$2,(F31*P31+$W$3*Q31)/24*$W$2)))</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="T31" s="59"/>
       <c r="U31" s="74" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="V31" s="23"/>
       <c r="W31" s="24"/>
     </row>
-    <row r="32" spans="1:23" ht="14.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:24" customHeight="1" ht="14.5">
       <c r="A32" s="20"/>
       <c r="B32" s="17"/>
       <c r="C32" s="15"/>
       <c r="D32" s="15"/>
       <c r="E32" s="16"/>
       <c r="F32" s="77">
-        <f t="shared" si="1"/>
+        <f>IF(G32="","",IF(G32="BA",100%,E32/G32))</f>
         <v>1</v>
       </c>
       <c r="G32" s="78" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(U32="","",IF(U32="BA","BA",U32))</f>
         <v>BA</v>
       </c>
       <c r="H32" s="17"/>
@@ -3058,44 +3041,44 @@
       <c r="M32" s="14"/>
       <c r="N32" s="69"/>
       <c r="O32" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(OR($K32="",$L32="",$M32=""),"",($K32+$L32)/SUM($K32:$M32))</f>
         <v/>
       </c>
       <c r="P32" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(K32="","",K32*24)</f>
         <v/>
       </c>
       <c r="Q32" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(L32="","",L32*24)</f>
         <v/>
       </c>
       <c r="R32" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="S32" s="25">
+        <f>IF(M32="","",M32*24)</f>
+        <v/>
+      </c>
+      <c r="S32" s="25" t="e">
         <f>IF(R32&gt;(24-6),0,IF((AND(P32=0,(COUNTIF(Q$6:Q32,24)+$W$4)&gt;10)),0,IF(U32="BA",(100%*P32+$W$3*Q32)/24*$W$2,(F32*P32+$W$3*Q32)/24*$W$2)))</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="T32" s="59"/>
       <c r="U32" s="74" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="V32" s="23"/>
       <c r="W32" s="24"/>
     </row>
-    <row r="33" spans="1:23" ht="14.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:24" customHeight="1" ht="14.5">
       <c r="A33" s="20"/>
       <c r="B33" s="17"/>
       <c r="C33" s="15"/>
       <c r="D33" s="15"/>
       <c r="E33" s="16"/>
       <c r="F33" s="77">
-        <f t="shared" si="1"/>
+        <f>IF(G33="","",IF(G33="BA",100%,E33/G33))</f>
         <v>1</v>
       </c>
       <c r="G33" s="78" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(U33="","",IF(U33="BA","BA",U33))</f>
         <v>BA</v>
       </c>
       <c r="H33" s="17"/>
@@ -3106,44 +3089,44 @@
       <c r="M33" s="14"/>
       <c r="N33" s="69"/>
       <c r="O33" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(OR($K33="",$L33="",$M33=""),"",($K33+$L33)/SUM($K33:$M33))</f>
         <v/>
       </c>
       <c r="P33" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(K33="","",K33*24)</f>
         <v/>
       </c>
       <c r="Q33" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(L33="","",L33*24)</f>
         <v/>
       </c>
       <c r="R33" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="S33" s="25">
+        <f>IF(M33="","",M33*24)</f>
+        <v/>
+      </c>
+      <c r="S33" s="25" t="e">
         <f>IF(R33&gt;(24-6),0,IF((AND(P33=0,(COUNTIF(Q$6:Q33,24)+$W$4)&gt;10)),0,IF(U33="BA",(100%*P33+$W$3*Q33)/24*$W$2,(F33*P33+$W$3*Q33)/24*$W$2)))</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="T33" s="59"/>
       <c r="U33" s="74" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="V33" s="23"/>
       <c r="W33" s="24"/>
     </row>
-    <row r="34" spans="1:23" ht="14.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:24" customHeight="1" ht="14.5">
       <c r="A34" s="20"/>
       <c r="B34" s="17"/>
       <c r="C34" s="15"/>
       <c r="D34" s="15"/>
       <c r="E34" s="16"/>
       <c r="F34" s="77">
-        <f t="shared" si="1"/>
+        <f>IF(G34="","",IF(G34="BA",100%,E34/G34))</f>
         <v>1</v>
       </c>
       <c r="G34" s="78" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(U34="","",IF(U34="BA","BA",U34))</f>
         <v>BA</v>
       </c>
       <c r="H34" s="17"/>
@@ -3154,44 +3137,44 @@
       <c r="M34" s="14"/>
       <c r="N34" s="69"/>
       <c r="O34" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(OR($K34="",$L34="",$M34=""),"",($K34+$L34)/SUM($K34:$M34))</f>
         <v/>
       </c>
       <c r="P34" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(K34="","",K34*24)</f>
         <v/>
       </c>
       <c r="Q34" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(L34="","",L34*24)</f>
         <v/>
       </c>
       <c r="R34" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="S34" s="25">
+        <f>IF(M34="","",M34*24)</f>
+        <v/>
+      </c>
+      <c r="S34" s="25" t="e">
         <f>IF(R34&gt;(24-6),0,IF((AND(P34=0,(COUNTIF(Q$6:Q34,24)+$W$4)&gt;10)),0,IF(U34="BA",(100%*P34+$W$3*Q34)/24*$W$2,(F34*P34+$W$3*Q34)/24*$W$2)))</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="T34" s="59"/>
       <c r="U34" s="74" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="V34" s="23"/>
       <c r="W34" s="24"/>
     </row>
-    <row r="35" spans="1:23" ht="14.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:24" customHeight="1" ht="14.5">
       <c r="A35" s="20"/>
       <c r="B35" s="17"/>
       <c r="C35" s="15"/>
       <c r="D35" s="15"/>
       <c r="E35" s="16"/>
       <c r="F35" s="77">
-        <f t="shared" si="1"/>
+        <f>IF(G35="","",IF(G35="BA",100%,E35/G35))</f>
         <v>1</v>
       </c>
       <c r="G35" s="78" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(U35="","",IF(U35="BA","BA",U35))</f>
         <v>BA</v>
       </c>
       <c r="H35" s="17"/>
@@ -3202,44 +3185,44 @@
       <c r="M35" s="14"/>
       <c r="N35" s="69"/>
       <c r="O35" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(OR($K35="",$L35="",$M35=""),"",($K35+$L35)/SUM($K35:$M35))</f>
         <v/>
       </c>
       <c r="P35" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(K35="","",K35*24)</f>
         <v/>
       </c>
       <c r="Q35" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(L35="","",L35*24)</f>
         <v/>
       </c>
       <c r="R35" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="S35" s="25">
+        <f>IF(M35="","",M35*24)</f>
+        <v/>
+      </c>
+      <c r="S35" s="25" t="e">
         <f>IF(R35&gt;(24-6),0,IF((AND(P35=0,(COUNTIF(Q$6:Q35,24)+$W$4)&gt;10)),0,IF(U35="BA",(100%*P35+$W$3*Q35)/24*$W$2,(F35*P35+$W$3*Q35)/24*$W$2)))</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="T35" s="59"/>
       <c r="U35" s="74" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="V35" s="23"/>
       <c r="W35" s="24"/>
     </row>
-    <row r="36" spans="1:23" ht="14.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:24" customHeight="1" ht="14.5">
       <c r="A36" s="36"/>
       <c r="B36" s="37"/>
       <c r="C36" s="38"/>
       <c r="D36" s="38"/>
       <c r="E36" s="39"/>
       <c r="F36" s="77">
-        <f t="shared" si="1"/>
+        <f>IF(G36="","",IF(G36="BA",100%,E36/G36))</f>
         <v>1</v>
       </c>
       <c r="G36" s="78" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(U36="","",IF(U36="BA","BA",U36))</f>
         <v>BA</v>
       </c>
       <c r="H36" s="37"/>
@@ -3250,35 +3233,35 @@
       <c r="M36" s="41"/>
       <c r="N36" s="70"/>
       <c r="O36" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(OR($K36="",$L36="",$M36=""),"",($K36+$L36)/SUM($K36:$M36))</f>
         <v/>
       </c>
       <c r="P36" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(K36="","",K36*24)</f>
         <v/>
       </c>
       <c r="Q36" s="66" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(L36="","",L36*24)</f>
         <v/>
       </c>
       <c r="R36" s="66" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="S36" s="25">
+        <f>IF(M36="","",M36*24)</f>
+        <v/>
+      </c>
+      <c r="S36" s="25" t="e">
         <f>IF(R36&gt;(24-6),0,IF((AND(P36=0,(COUNTIF(Q$6:Q36,24)+$W$4)&gt;10)),0,IF(U36="BA",(100%*P36+$W$3*Q36)/24*$W$2,(F36*P36+$W$3*Q36)/24*$W$2)))</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="T36" s="61"/>
       <c r="U36" s="74" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="V36" s="23"/>
       <c r="W36" s="24"/>
     </row>
-    <row r="37" spans="1:23" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:24" customHeight="1" ht="20.15">
       <c r="A37" s="42" t="s">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="B37" s="43"/>
       <c r="C37" s="43"/>
@@ -3329,7 +3312,7 @@
     </row>
   </sheetData>
   <sheetProtection formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <mergeCells count="6">
+  <mergeCells>
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="A2:T2"/>
     <mergeCell ref="A4:A5"/>
@@ -3337,13 +3320,13 @@
     <mergeCell ref="P4:R4"/>
     <mergeCell ref="T4:T5"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="U6:U36" xr:uid="{1F670E5D-A7FD-4F17-BF5F-7BFE38AF2C35}">
+  <dataValidations count="1">
+    <dataValidation type="list" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="0" sqref="U6:U36">
       <formula1>"BA"</formula1>
     </dataValidation>
   </dataValidations>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="43" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true"/>
+  <pageMargins left="0.39370078740157" right="0.39370078740157" top="0.59055118110236" bottom="0.59055118110236" header="0.31496062992126" footer="0.31496062992126"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="43" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" r:id="rId1ps"/>
 </worksheet>
 </file>